--- a/Archivos_Compartidos/Excel/POSICION.xlsx
+++ b/Archivos_Compartidos/Excel/POSICION.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Reportes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1D6F9158-A902-4D33-B528-CAF1C51BA400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F3D068-ACC8-41B1-862B-DCC1AA67DD13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="151">
   <si>
     <t>Frecuencia</t>
   </si>
@@ -463,6 +463,30 @@
   </si>
   <si>
     <t>MX1037540</t>
+  </si>
+  <si>
+    <t>MX1013407</t>
+  </si>
+  <si>
+    <t>MABE</t>
+  </si>
+  <si>
+    <t>MX00001573</t>
+  </si>
+  <si>
+    <t>MX000015731</t>
+  </si>
+  <si>
+    <t>MX00001940</t>
+  </si>
+  <si>
+    <t>MX000015732</t>
+  </si>
+  <si>
+    <t>ISSSSPEA</t>
+  </si>
+  <si>
+    <t>MX1030019</t>
   </si>
 </sst>
 </file>
@@ -506,7 +530,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -537,6 +561,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -553,7 +595,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
@@ -585,6 +627,22 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -598,6 +656,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -918,7 +985,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Hoja4"/>
-  <dimension ref="A1:Y15"/>
+  <dimension ref="A1:AH15"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.5546875" style="1" bestFit="1" customWidth="1"/>
@@ -931,99 +998,129 @@
     <col min="11" max="11" width="11.44140625" style="12"/>
     <col min="12" max="12" width="12" style="12" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.44140625" style="1"/>
-    <col min="14" max="14" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="25" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="13.5546875" style="1" customWidth="1"/>
-    <col min="20" max="16384" width="11.44140625" style="1"/>
+    <col min="14" max="15" width="11.44140625" style="16"/>
+    <col min="16" max="16" width="11.44140625" style="1"/>
+    <col min="17" max="18" width="12.6640625" style="18" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.44140625" style="1"/>
+    <col min="20" max="21" width="12.6640625" style="22" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.44140625" style="1"/>
+    <col min="23" max="23" width="12.5546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="19.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="25" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="28" width="13.5546875" style="1" customWidth="1"/>
+    <col min="29" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16"/>
-      <c r="E1" s="17" t="s">
+      <c r="C1" s="24"/>
+      <c r="E1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="17"/>
-      <c r="H1" s="18" t="s">
+      <c r="F1" s="25"/>
+      <c r="H1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="18"/>
-      <c r="K1" s="19" t="s">
+      <c r="I1" s="26"/>
+      <c r="K1" s="27" t="s">
         <v>2</v>
       </c>
-      <c r="L1" s="19"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="U1" s="1" t="s">
+      <c r="L1" s="27"/>
+      <c r="N1" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="O1" s="28"/>
+      <c r="Q1" s="29" t="s">
+        <v>2</v>
+      </c>
+      <c r="R1" s="29"/>
+      <c r="T1" s="30" t="s">
+        <v>2</v>
+      </c>
+      <c r="U1" s="30"/>
+      <c r="W1" s="23"/>
+      <c r="X1" s="23"/>
+      <c r="Y1" s="23"/>
+      <c r="AD1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="V1" s="1" t="s">
+      <c r="AE1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="X1" s="1" t="s">
+      <c r="AG1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="AH1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:34" ht="16.8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="16"/>
-      <c r="E2" s="17" t="s">
+      <c r="C2" s="24"/>
+      <c r="E2" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="17"/>
-      <c r="H2" s="18" t="s">
+      <c r="F2" s="25"/>
+      <c r="H2" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="18"/>
-      <c r="K2" s="19" t="s">
+      <c r="I2" s="26"/>
+      <c r="K2" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="19"/>
-      <c r="N2" s="1" t="s">
+      <c r="L2" s="27"/>
+      <c r="N2" s="28">
+        <v>1013407</v>
+      </c>
+      <c r="O2" s="28"/>
+      <c r="Q2" s="29" t="s">
+        <v>144</v>
+      </c>
+      <c r="R2" s="29"/>
+      <c r="T2" s="30" t="s">
+        <v>149</v>
+      </c>
+      <c r="U2" s="30"/>
+      <c r="W2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Y2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="AA2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="AB2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="AD2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="AE2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="W2" s="4"/>
-      <c r="X2" s="1" t="s">
+      <c r="AF2" s="4"/>
+      <c r="AG2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="AH2" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:34" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>20</v>
       </c>
@@ -1051,29 +1148,47 @@
       <c r="L3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="N3" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="O3" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q3" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="R3" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="T3" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="U3" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="W3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="X3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="Y3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="AA3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="AB3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X3" s="1" t="s">
+      <c r="AG3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="Y3" s="1" t="s">
+      <c r="AH3" s="1" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:34" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B4" s="9" t="s">
         <v>29</v>
       </c>
@@ -1098,24 +1213,42 @@
       <c r="L4" s="12">
         <v>65502898380</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="N4" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="O4" s="16">
+        <v>1013407</v>
+      </c>
+      <c r="Q4" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="R4" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="T4" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="U4" s="22" t="s">
+        <v>150</v>
+      </c>
+      <c r="W4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="X4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="Y4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="R4" s="1" t="s">
+      <c r="AA4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="AB4" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="U4" s="13"/>
-    </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+      <c r="AD4" s="13"/>
+    </row>
+    <row r="5" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B5" s="9" t="s">
         <v>35</v>
       </c>
@@ -1134,20 +1267,26 @@
       <c r="L5" s="12">
         <v>65502898437</v>
       </c>
-      <c r="N5" s="1" t="s">
+      <c r="Q5" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="R5" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="W5" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="X5" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="R5" s="1" t="s">
+      <c r="AA5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="S5" s="1" t="s">
+      <c r="AB5" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B6" s="9" t="s">
         <v>42</v>
       </c>
@@ -1160,154 +1299,166 @@
       <c r="L6" s="12">
         <v>65507298252</v>
       </c>
-      <c r="N6" s="1" t="s">
+      <c r="Q6" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="R6" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="W6" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="O6" s="1" t="s">
+      <c r="X6" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="R6" s="1" t="s">
+      <c r="AA6" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="S6" s="1" t="s">
+      <c r="AB6" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B7" s="9" t="s">
         <v>47</v>
       </c>
       <c r="C7" s="9">
         <v>1018695</v>
       </c>
-      <c r="N7" s="1" t="s">
+      <c r="Q7" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="R7" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="W7" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="O7" s="1" t="s">
+      <c r="X7" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="P7" s="1" t="s">
+      <c r="Y7" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B8" s="9" t="s">
         <v>51</v>
       </c>
       <c r="C8" s="9">
         <v>2111039</v>
       </c>
-      <c r="N8" s="1" t="s">
+      <c r="W8" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="O8" s="1" t="s">
+      <c r="X8" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="P8" s="1" t="s">
+      <c r="Y8" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B9" s="9" t="s">
         <v>54</v>
       </c>
       <c r="C9" s="9">
         <v>2111047</v>
       </c>
-      <c r="N9" s="1" t="s">
+      <c r="W9" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="O9" s="1" t="s">
+      <c r="X9" s="1" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B10" s="9" t="s">
         <v>57</v>
       </c>
       <c r="C10" s="9">
         <v>2141256</v>
       </c>
-      <c r="N10" s="1" t="s">
+      <c r="W10" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="O10" s="1" t="s">
+      <c r="X10" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B11" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C11" s="9">
         <v>2141264</v>
       </c>
-      <c r="N11" s="1" t="s">
+      <c r="W11" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="O11" s="1" t="s">
+      <c r="X11" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B12" s="9" t="s">
         <v>63</v>
       </c>
       <c r="C12" s="9">
         <v>72636</v>
       </c>
-      <c r="N12" s="1" t="s">
+      <c r="W12" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="O12" s="1" t="s">
+      <c r="X12" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B13" s="9" t="s">
         <v>66</v>
       </c>
       <c r="C13" s="9">
         <v>72637</v>
       </c>
-      <c r="N13" s="1" t="s">
+      <c r="W13" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="O13" s="1" t="s">
+      <c r="X13" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B14" s="9" t="s">
         <v>69</v>
       </c>
       <c r="C14" s="9">
         <v>75016</v>
       </c>
-      <c r="N14" s="1" t="s">
+      <c r="W14" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="O14" s="1" t="s">
+      <c r="X14" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.3">
       <c r="B15" s="9" t="s">
         <v>72</v>
       </c>
       <c r="C15" s="9">
         <v>75017</v>
       </c>
-      <c r="N15" s="1" t="s">
+      <c r="W15" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="O15" s="1" t="s">
+      <c r="X15" s="1" t="s">
         <v>68</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="N1:P1"/>
+  <mergeCells count="15">
+    <mergeCell ref="W1:Y1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="E2:F2"/>
     <mergeCell ref="H2:I2"/>
@@ -1316,6 +1467,12 @@
     <mergeCell ref="E1:F1"/>
     <mergeCell ref="H1:I1"/>
     <mergeCell ref="K1:L1"/>
+    <mergeCell ref="N1:O1"/>
+    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="T1:U1"/>
+    <mergeCell ref="T2:U2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -1749,7 +1906,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" s="14" t="s">
         <v>124</v>
       </c>
@@ -1760,7 +1917,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" s="14" t="s">
         <v>125</v>
       </c>
@@ -1771,7 +1928,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>126</v>
       </c>
@@ -1782,7 +1939,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" s="14" t="s">
         <v>127</v>
       </c>
@@ -1793,7 +1950,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>128</v>
       </c>
@@ -1804,7 +1961,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" s="14" t="s">
         <v>129</v>
       </c>
@@ -1815,7 +1972,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" s="14" t="s">
         <v>130</v>
       </c>
@@ -1826,7 +1983,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" s="14" t="s">
         <v>131</v>
       </c>
@@ -1837,7 +1994,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" s="14" t="s">
         <v>132</v>
       </c>
@@ -1848,7 +2005,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A48" s="14" t="s">
         <v>133</v>
       </c>
@@ -1859,7 +2016,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A49" s="14" t="s">
         <v>134</v>
       </c>
@@ -1870,7 +2027,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A50" s="14" t="s">
         <v>135</v>
       </c>
@@ -1881,7 +2038,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A51" s="14" t="s">
         <v>136</v>
       </c>
@@ -1892,7 +2049,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A52" s="14" t="s">
         <v>138</v>
       </c>
@@ -1903,7 +2060,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A53" s="14" t="s">
         <v>139</v>
       </c>
@@ -1914,7 +2071,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A54" s="14" t="s">
         <v>140</v>
       </c>
@@ -1925,7 +2082,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A55" s="14" t="s">
         <v>141</v>
       </c>
@@ -1936,7 +2093,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="15" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="C56" s="1"/>

--- a/Archivos_Compartidos/Excel/POSICION.xlsx
+++ b/Archivos_Compartidos/Excel/POSICION.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Reportes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10F3D068-ACC8-41B1-862B-DCC1AA67DD13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E33ACC7-F5E4-4D31-89E3-155A92D7857F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="I1" s="26"/>
       <c r="K1" s="27" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L1" s="27"/>
       <c r="N1" s="28" t="s">
